--- a/3_PPTurnover/input/dict/DictOfPhaseout.xlsx
+++ b/3_PPTurnover/input/dict/DictOfPhaseout.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\92978\Desktop\Unit-level-Turnover-Model-main\3_PPTurnover\input\dict\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\92978\Desktop\Unit-level-Turnover-Model\3_PPTurnover\input\dict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AB9A14-EA03-40AE-87D9-CF5308412D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C5D350-87F2-4923-B1A9-2509D1DF96C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11438" yWindow="0" windowWidth="11684" windowHeight="13763" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Max_Load_Life" sheetId="1" r:id="rId1"/>
+    <sheet name="Readme" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
     <author>Yxz_哲</author>
   </authors>
   <commentList>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{A51675E4-40D0-4AD3-A1FD-EC8DD30D50AF}">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{A51675E4-40D0-4AD3-A1FD-EC8DD30D50AF}">
       <text>
         <r>
           <rPr>
@@ -70,17 +71,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Sector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LifeTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OverAgedPhaseOutInYear</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -91,12 +84,16 @@
     <t>Coal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>This file assumes a standard size of 2 × 600 MW for newly built power plants, equivalent to maximum 5,256,000 MWh of annual generation.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +123,12 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -135,7 +138,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -143,12 +146,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -429,39 +449,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>40</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
+      <c r="B2" s="2">
         <f>600*8760</f>
         <v>5256000</v>
       </c>
@@ -471,4 +479,20 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A350DAB0-BC73-4C73-B81C-E3203E8BCFCB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>